--- a/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,85</t>
+          <t>-1,42; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,46</t>
+          <t>3,93; 10,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,98; 21,83</t>
+          <t>13,46; 21,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,93</t>
+          <t>-1,33; 4,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,58</t>
+          <t>2,07; 8,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,45; 24,08</t>
+          <t>17,06; 23,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,46</t>
+          <t>-0,47; 3,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 8,56</t>
+          <t>3,66; 8,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,34; 22,15</t>
+          <t>17,05; 22,02</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 45,33</t>
+          <t>-13,5; 46,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,39; 121,1</t>
+          <t>35,4; 122,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128,35; 256,87</t>
+          <t>122,5; 264,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 29,66</t>
+          <t>-7,95; 33,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 62,62</t>
+          <t>12,49; 63,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>105,93; 178,12</t>
+          <t>103,46; 180,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 30,32</t>
+          <t>-3,62; 31,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>28,1; 71,96</t>
+          <t>27,79; 74,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>128,65; 190,54</t>
+          <t>124,33; 189,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 2,33</t>
+          <t>-0,83; 2,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,96</t>
+          <t>2,54; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 12,02</t>
+          <t>4,47; 12,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,21</t>
+          <t>-0,79; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,29</t>
+          <t>4,04; 7,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,39; 8,32</t>
+          <t>3,45; 8,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,8</t>
+          <t>-0,45; 1,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,29</t>
+          <t>3,71; 6,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 9,7</t>
+          <t>5,44; 9,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 50,35</t>
+          <t>-13,54; 56,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,47; 128,74</t>
+          <t>38,61; 137,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87,22; 253,84</t>
+          <t>84,96; 257,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 70,97</t>
+          <t>-17,38; 67,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,28; 228,68</t>
+          <t>82,06; 234,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,5; 251,41</t>
+          <t>80,04; 253,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 42,56</t>
+          <t>-8,55; 42,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,14; 152,72</t>
+          <t>70,75; 152,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>104,38; 223,72</t>
+          <t>106,72; 225,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 7,3</t>
+          <t>-0,85; 7,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,02</t>
+          <t>5,08; 13,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 10,37</t>
+          <t>2,24; 9,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 7,47</t>
+          <t>-0,6; 7,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 8,68</t>
+          <t>1,24; 9,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 10,29</t>
+          <t>4,1; 10,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,27</t>
+          <t>0,91; 6,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,07; 9,9</t>
+          <t>4,22; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 9,15</t>
+          <t>4,3; 9,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 99,77</t>
+          <t>-9,39; 97,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,76; 193,45</t>
+          <t>44,84; 196,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,55; 151,75</t>
+          <t>18,32; 143,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 121,96</t>
+          <t>-8,71; 125,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,78; 143,16</t>
+          <t>12,09; 151,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,12; 171,31</t>
+          <t>42,73; 188,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 90,75</t>
+          <t>8,94; 88,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43,85; 141,86</t>
+          <t>42,95; 146,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,35; 128,15</t>
+          <t>44,68; 136,05</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,41</t>
+          <t>-0,51; 2,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,9</t>
+          <t>3,66; 6,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,46</t>
+          <t>5,87; 11,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,53</t>
+          <t>-0,44; 2,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,89</t>
+          <t>2,94; 5,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,52; 9,56</t>
+          <t>4,64; 9,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,95</t>
+          <t>0,15; 2,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,84</t>
+          <t>3,77; 5,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,89</t>
+          <t>6,2; 9,88</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 35,88</t>
+          <t>-6,57; 34,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,09; 103,68</t>
+          <t>44,17; 101,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76,66; 169,3</t>
+          <t>80,72; 173,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 30,51</t>
+          <t>-4,36; 31,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,32; 72,74</t>
+          <t>30,55; 73,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>49,82; 118,56</t>
+          <t>55,42; 117,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,76; 25,21</t>
+          <t>1,81; 29,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,64; 77,05</t>
+          <t>44,02; 78,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>73,7; 128,84</t>
+          <t>76,33; 130,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,74</t>
+          <t>18,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,54</t>
+          <t>19,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19,58</t>
+          <t>19,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 3,86</t>
+          <t>-1,45; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 10,34</t>
+          <t>3,8; 10,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,46; 21,78</t>
+          <t>14,25; 22,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 4,47</t>
+          <t>-1,43; 4,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,81</t>
+          <t>1,92; 8,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,06; 23,82</t>
+          <t>16,38; 22,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,62</t>
+          <t>-0,67; 3,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,65</t>
+          <t>3,98; 8,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 22,02</t>
+          <t>16,97; 22,34</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>183,64%</t>
+          <t>192,06%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>137,75%</t>
+          <t>133,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>155,41%</t>
+          <t>154,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 46,85</t>
+          <t>-13,52; 43,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,4; 122,25</t>
+          <t>35,24; 121,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>122,5; 264,41</t>
+          <t>131,34; 268,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 33,29</t>
+          <t>-8,61; 30,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 63,96</t>
+          <t>11,41; 64,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>103,46; 180,16</t>
+          <t>98,11; 170,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 31,36</t>
+          <t>-4,79; 29,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,79; 74,94</t>
+          <t>30,0; 74,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,33; 189,94</t>
+          <t>124,62; 192,77</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,37</t>
+          <t>11,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,4</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,89</t>
+          <t>9,68</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,51</t>
+          <t>-0,79; 2,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,23</t>
+          <t>2,54; 6,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 12,17</t>
+          <t>9,57; 13,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,16</t>
+          <t>-0,87; 2,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,42</t>
+          <t>4,02; 7,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,48</t>
+          <t>6,43; 9,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,77</t>
+          <t>-0,45; 1,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,21</t>
+          <t>3,8; 6,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 9,71</t>
+          <t>8,46; 10,98</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173,58%</t>
+          <t>211,13%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>161,16%</t>
+          <t>200,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>167,55%</t>
+          <t>205,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 56,28</t>
+          <t>-13,46; 47,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>38,61; 137,58</t>
+          <t>41,5; 138,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>84,96; 257,55</t>
+          <t>151,96; 298,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 67,29</t>
+          <t>-20,99; 69,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>82,06; 234,92</t>
+          <t>82,98; 221,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,04; 253,31</t>
+          <t>133,12; 296,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 42,37</t>
+          <t>-8,79; 45,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,75; 152,95</t>
+          <t>72,3; 150,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>106,72; 225,46</t>
+          <t>159,37; 266,02</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,76</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,35</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,81</t>
+          <t>6,91</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 7,16</t>
+          <t>-0,79; 7,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 13,59</t>
+          <t>4,57; 13,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 9,86</t>
+          <t>2,78; 10,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 7,56</t>
+          <t>-0,52; 7,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,13</t>
+          <t>1,03; 9,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,85</t>
+          <t>3,9; 10,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,26</t>
+          <t>0,81; 6,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 9,91</t>
+          <t>4,19; 10,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,35</t>
+          <t>4,29; 9,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 97,72</t>
+          <t>-9,65; 98,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44,84; 196,68</t>
+          <t>40,71; 184,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,32; 143,31</t>
+          <t>25,89; 157,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 125,79</t>
+          <t>-5,64; 131,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,09; 151,43</t>
+          <t>8,95; 147,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42,73; 188,28</t>
+          <t>36,55; 183,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,94; 88,93</t>
+          <t>7,98; 89,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>42,95; 146,5</t>
+          <t>41,73; 137,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,68; 136,05</t>
+          <t>45,94; 136,51</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9,4</t>
+          <t>11,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,65</t>
+          <t>8,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>9,93</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 2,25</t>
+          <t>-0,35; 2,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,8</t>
+          <t>3,89; 6,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,46</t>
+          <t>9,62; 12,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,52</t>
+          <t>-0,36; 2,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,9</t>
+          <t>2,77; 5,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 9,36</t>
+          <t>7,38; 10,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,12</t>
+          <t>0,07; 2,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,94</t>
+          <t>3,71; 5,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,88</t>
+          <t>8,86; 11,05</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>129,08%</t>
+          <t>152,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>100,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105,94%</t>
+          <t>123,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 34,24</t>
+          <t>-4,62; 35,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>44,17; 101,0</t>
+          <t>48,68; 104,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,72; 173,25</t>
+          <t>121,97; 195,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 31,11</t>
+          <t>-3,81; 30,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>30,55; 73,15</t>
+          <t>29,01; 74,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,42; 117,05</t>
+          <t>75,44; 126,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 29,06</t>
+          <t>0,61; 27,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>44,02; 78,33</t>
+          <t>43,5; 78,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,33; 130,82</t>
+          <t>103,52; 147,32</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales</t>
+          <t>Población que conforma un hogar unipersonal</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
